--- a/data/b_Optimierung/Verkehrswende_opt_speicher_statistiken.xlsx
+++ b/data/b_Optimierung/Verkehrswende_opt_speicher_statistiken.xlsx
@@ -1,37 +1,100 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HansisRasanterRaser\Desktop\UNI\000_DA\git\knEBiD\data\b_Optimierung\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FA8C3E-041D-48B7-89A6-1AFF6ED3FB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Speicher_Statistiken" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Speicher_Statistiken" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+  <si>
+    <t>Speicher</t>
+  </si>
+  <si>
+    <t>Zeitschritte</t>
+  </si>
+  <si>
+    <t>Kapazität [MWh]</t>
+  </si>
+  <si>
+    <t>Max SOC [MWh]</t>
+  </si>
+  <si>
+    <t>Min SOC [MWh]</t>
+  </si>
+  <si>
+    <t>Durchschn. SOC [MWh]</t>
+  </si>
+  <si>
+    <t>Max Entladung [MW]</t>
+  </si>
+  <si>
+    <t>Max Ladung [MW]</t>
+  </si>
+  <si>
+    <t>Gesamte Entladung [MWh]</t>
+  </si>
+  <si>
+    <t>Gesamte Ladung [MWh]</t>
+  </si>
+  <si>
+    <t>Batteriespeicher_Batterie</t>
+  </si>
+  <si>
+    <t>Pumpspeicher_Pump</t>
+  </si>
+  <si>
+    <t>Wasserstoffkaverne_H2</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +109,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,166 +433,187 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Speicher</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Zeitschritte</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Kapazität [MWh]</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Max SOC [MWh]</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Min SOC [MWh]</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Durchschn. SOC [MWh]</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Max Entladung [MW]</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Max Ladung [MW]</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Gesamte Entladung [MWh]</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Gesamte Ladung [MWh]</t>
-        </is>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Batteriespeicher_Batterie</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
         <v>35036</v>
       </c>
-      <c r="C2" t="n">
-        <v>38796.02</v>
-      </c>
-      <c r="D2" t="n">
-        <v>38796.02</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="C2">
+        <v>44861.358999999997</v>
+      </c>
+      <c r="D2">
+        <v>44861.358999999997</v>
+      </c>
+      <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
-        <v>2150.522891325269</v>
-      </c>
-      <c r="G2" t="n">
-        <v>19398.01</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-19398.01</v>
-      </c>
-      <c r="I2" t="n">
-        <v>18836906.19514589</v>
-      </c>
-      <c r="J2" t="n">
-        <v>18832056.68995875</v>
+      <c r="F2">
+        <v>2491.7037354314152</v>
+      </c>
+      <c r="G2">
+        <v>22430.68</v>
+      </c>
+      <c r="H2">
+        <v>-22430.68</v>
+      </c>
+      <c r="I2">
+        <v>21087367.965659559</v>
+      </c>
+      <c r="J2">
+        <v>21081760.29475658</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Pumpspeicher_Pump</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
         <v>8759</v>
       </c>
-      <c r="C3" t="n">
-        <v>187806.38</v>
-      </c>
-      <c r="D3" t="n">
-        <v>187806.38</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-1.208083e-11</v>
-      </c>
-      <c r="F3" t="n">
-        <v>41187.18214108346</v>
-      </c>
-      <c r="G3" t="n">
-        <v>18780.638</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-18780.638</v>
-      </c>
-      <c r="I3" t="n">
-        <v>13915323.68956</v>
-      </c>
-      <c r="J3" t="n">
-        <v>13914384.67816475</v>
+      <c r="C3">
+        <v>259713.5</v>
+      </c>
+      <c r="D3">
+        <v>259713.5</v>
+      </c>
+      <c r="E3">
+        <v>-2.6878922E-11</v>
+      </c>
+      <c r="F3">
+        <v>57102.450429145567</v>
+      </c>
+      <c r="G3">
+        <v>25971.35</v>
+      </c>
+      <c r="H3">
+        <v>-25971.35</v>
+      </c>
+      <c r="I3">
+        <v>19352990.851023391</v>
+      </c>
+      <c r="J3">
+        <v>19351692.285475139</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wasserstoffkaverne_H2</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
         <v>8759</v>
       </c>
-      <c r="C4" t="n">
-        <v>40604905</v>
-      </c>
-      <c r="D4" t="n">
-        <v>26701441</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="C4">
+        <v>42802222</v>
+      </c>
+      <c r="D4">
+        <v>28350399</v>
+      </c>
+      <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" t="n">
-        <v>13197809.55636876</v>
-      </c>
-      <c r="G4" t="n">
-        <v>160195.31</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-160195.31</v>
-      </c>
-      <c r="I4" t="n">
-        <v>75997985.4618005</v>
-      </c>
-      <c r="J4" t="n">
-        <v>76013769.75431733</v>
+      <c r="F4">
+        <v>14089307.338249691</v>
+      </c>
+      <c r="G4">
+        <v>172275.8</v>
+      </c>
+      <c r="H4">
+        <v>-172275.8</v>
+      </c>
+      <c r="I4">
+        <v>84688505.685736075</v>
+      </c>
+      <c r="J4">
+        <v>84704621.160470799</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C6">
+        <f>C2/1000</f>
+        <v>44.861359</v>
+      </c>
+      <c r="D6">
+        <v>57.01</v>
+      </c>
+      <c r="E6">
+        <f>C6/D6</f>
+        <v>0.78690333274864066</v>
+      </c>
+      <c r="F6">
+        <f>1-E6</f>
+        <v>0.21309666725135934</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C7">
+        <f t="shared" ref="C7:C8" si="0">C3/1000</f>
+        <v>259.71350000000001</v>
+      </c>
+      <c r="D7">
+        <v>304.3</v>
+      </c>
+      <c r="E7">
+        <f t="shared" ref="E7:E8" si="1">C7/D7</f>
+        <v>0.85347847518895825</v>
+      </c>
+      <c r="F7">
+        <f t="shared" ref="F7:F8" si="2">1-E7</f>
+        <v>0.14652152481104175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>42802.222000000002</v>
+      </c>
+      <c r="D8">
+        <v>49457.4</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>0.86543615313380806</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="2"/>
+        <v>0.13456384686619194</v>
       </c>
     </row>
   </sheetData>
